--- a/gaming_forms/029_game_concept_upload_form--gaming_forms.xlsx
+++ b/gaming_forms/029_game_concept_upload_form--gaming_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_developer</t>
+          <t>game_concept_upload_form_game_developer_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Game Developer</t>
+          <t>Game Concept Upload Form Game Developer 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_upload_file</t>
+          <t>game_concept_upload_form_upload_file_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Upload File</t>
+          <t>Game Concept Upload Form Upload File 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_upload_file</t>
+          <t>game_concept_upload_form_upload_file_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Upload File</t>
+          <t>Game Concept Upload Form Upload File 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_reviewer_name</t>
+          <t>game_concept_upload_form_reviewer_name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reviewer Name</t>
+          <t>Game Concept Upload Form Reviewer Name 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_reviewer_email</t>
+          <t>game_concept_upload_form_reviewer_email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reviewer Email</t>
+          <t>Game Concept Upload Form Reviewer Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_reviewer_phone</t>
+          <t>game_concept_upload_form_reviewer_phone_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reviewer Phone</t>
+          <t>Game Concept Upload Form Reviewer Phone 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_development_status</t>
+          <t>game_concept_upload_form_game_development_status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Game Development Status</t>
+          <t>Game Concept Upload Form Game Development Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_submit_date</t>
+          <t>game_concept_upload_form_submit_date_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submit Date</t>
+          <t>Game Concept Upload Form Submit Date 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_developer_choices</t>
+          <t>game_concept_upload_form_game_developer_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_developer_choices</t>
+          <t>game_concept_upload_form_game_developer_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_developer_choices</t>
+          <t>game_concept_upload_form_game_developer_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_development_status_choices</t>
+          <t>game_concept_upload_form_game_development_status_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_development_status_choices</t>
+          <t>game_concept_upload_form_game_development_status_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_development_status_choices</t>
+          <t>game_concept_upload_form_game_development_status_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>game_concept_upload_form_game_development_status_choices</t>
+          <t>game_concept_upload_form_game_development_status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
